--- a/Fichero-venta-2026.xlsx
+++ b/Fichero-venta-2026.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\PDL Nosotros\Contabilidad 2026\Ventas Enero-Junio-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AB2DDE8-86ED-448C-B952-9725D513642C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34E7F39-4743-429B-895A-C7142B540BD6}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="232">
   <si>
     <t>ENERO</t>
   </si>
@@ -725,11 +725,35 @@
   <si>
     <t>Total del costo</t>
   </si>
+  <si>
+    <t>julio</t>
+  </si>
+  <si>
+    <t>barro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Maceta jardinera 6" </t>
+  </si>
+  <si>
+    <t>Colchita de cocina</t>
+  </si>
+  <si>
+    <t>Estuche transparente</t>
+  </si>
+  <si>
+    <t>Reguilete</t>
+  </si>
+  <si>
+    <t>Pulso de señora</t>
+  </si>
+  <si>
+    <t>Comedero de perrito</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1068,24 +1092,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla2" displayName="Tabla2" ref="A1:K450" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K450"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla2" displayName="Tabla2" ref="A1:K491" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K491" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="Mes" dataDxfId="10"/>
-    <tableColumn id="2" name="Tipo" dataDxfId="9"/>
-    <tableColumn id="3" name="Articulo" dataDxfId="8"/>
-    <tableColumn id="4" name="Cant" dataDxfId="7"/>
-    <tableColumn id="5" name="Precio de costo" dataDxfId="6"/>
-    <tableColumn id="6" name="Valor de venta" dataDxfId="5"/>
-    <tableColumn id="7" name="Vendido " dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Mes" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Articulo" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Cant" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Precio de costo" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Valor de venta" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Vendido " dataDxfId="4">
       <calculatedColumnFormula>D2*F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="Ganancia despues de impuesto de venta" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Ganancia despues de impuesto de venta" dataDxfId="3">
       <calculatedColumnFormula>((F2-E2)*D2)-(G2*0.1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" name="Ganancia antes de impuesto de venta" dataDxfId="2"/>
-    <tableColumn id="10" name="Impuesto de venta" dataDxfId="1"/>
-    <tableColumn id="11" name="Total del costo" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Ganancia antes de impuesto de venta" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Impuesto de venta" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Total del costo" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1387,8 +1411,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K450"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K491"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
@@ -7091,15 +7115,15 @@
         <v>240</v>
       </c>
       <c r="I143" s="7">
-        <f t="shared" ref="I143:I160" si="33">(F143-E143)*D143</f>
+        <f t="shared" ref="I143:I158" si="33">(F143-E143)*D143</f>
         <v>300</v>
       </c>
       <c r="J143" s="7">
-        <f t="shared" ref="J143:J160" si="34">G143*0.1</f>
+        <f t="shared" ref="J143:J158" si="34">G143*0.1</f>
         <v>60</v>
       </c>
       <c r="K143" s="7">
-        <f t="shared" ref="K143:K160" si="35">D143*E143</f>
+        <f t="shared" ref="K143:K158" si="35">D143*E143</f>
         <v>300</v>
       </c>
     </row>
@@ -14082,7 +14106,7 @@
         <v>92</v>
       </c>
       <c r="I318" s="7">
-        <f t="shared" ref="I318:I332" si="69">(F318-E318)*D318</f>
+        <f t="shared" ref="I318:I330" si="69">(F318-E318)*D318</f>
         <v>130</v>
       </c>
       <c r="J318" s="7">
@@ -17901,7 +17925,7 @@
         <v>500</v>
       </c>
       <c r="H415" s="7">
-        <f t="shared" ref="H415:H450" si="92">((F415-E415)*D415)-(G415*0.1)</f>
+        <f t="shared" ref="H415:H478" si="92">((F415-E415)*D415)-(G415*0.1)</f>
         <v>50</v>
       </c>
       <c r="I415" s="7">
@@ -19309,6 +19333,1640 @@
       <c r="K450" s="7">
         <f t="shared" si="99"/>
         <v>150</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A451" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B451" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C451" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D451" s="7">
+        <v>1</v>
+      </c>
+      <c r="E451" s="7">
+        <v>700</v>
+      </c>
+      <c r="F451" s="7">
+        <v>1200</v>
+      </c>
+      <c r="G451" s="7">
+        <f>D451*F451</f>
+        <v>1200</v>
+      </c>
+      <c r="H451" s="7">
+        <f t="shared" si="92"/>
+        <v>380</v>
+      </c>
+      <c r="I451" s="7">
+        <f t="shared" ref="I451:I489" si="100">(F451-E451)*D451</f>
+        <v>500</v>
+      </c>
+      <c r="J451" s="7">
+        <f t="shared" ref="J451:J489" si="101">G451*0.1</f>
+        <v>120</v>
+      </c>
+      <c r="K451" s="7">
+        <f t="shared" ref="K451:K488" si="102">D451*E451</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A452" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B452" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C452" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D452" s="7">
+        <v>2</v>
+      </c>
+      <c r="E452" s="7">
+        <v>700</v>
+      </c>
+      <c r="F452" s="7">
+        <v>900</v>
+      </c>
+      <c r="G452" s="7">
+        <f t="shared" ref="G452:G461" si="103">D452*F452</f>
+        <v>1800</v>
+      </c>
+      <c r="H452" s="7">
+        <f t="shared" si="92"/>
+        <v>220</v>
+      </c>
+      <c r="I452" s="7">
+        <f t="shared" si="100"/>
+        <v>400</v>
+      </c>
+      <c r="J452" s="7">
+        <f t="shared" si="101"/>
+        <v>180</v>
+      </c>
+      <c r="K452" s="7">
+        <f t="shared" si="102"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A453" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B453" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C453" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D453" s="7">
+        <v>4</v>
+      </c>
+      <c r="E453" s="7">
+        <v>150</v>
+      </c>
+      <c r="F453" s="7">
+        <v>300</v>
+      </c>
+      <c r="G453" s="7">
+        <f t="shared" si="103"/>
+        <v>1200</v>
+      </c>
+      <c r="H453" s="7">
+        <f t="shared" si="92"/>
+        <v>480</v>
+      </c>
+      <c r="I453" s="7">
+        <f t="shared" si="100"/>
+        <v>600</v>
+      </c>
+      <c r="J453" s="7">
+        <f t="shared" si="101"/>
+        <v>120</v>
+      </c>
+      <c r="K453" s="7">
+        <f t="shared" si="102"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A454" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B454" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D454" s="7">
+        <v>1</v>
+      </c>
+      <c r="E454" s="7">
+        <v>350</v>
+      </c>
+      <c r="F454" s="7">
+        <v>550</v>
+      </c>
+      <c r="G454" s="7">
+        <f t="shared" si="103"/>
+        <v>550</v>
+      </c>
+      <c r="H454" s="7">
+        <f t="shared" si="92"/>
+        <v>145</v>
+      </c>
+      <c r="I454" s="7">
+        <f t="shared" si="100"/>
+        <v>200</v>
+      </c>
+      <c r="J454" s="7">
+        <f t="shared" si="101"/>
+        <v>55</v>
+      </c>
+      <c r="K454" s="7">
+        <f t="shared" si="102"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A455" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B455" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C455" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D455" s="7">
+        <v>1</v>
+      </c>
+      <c r="E455" s="7">
+        <v>150</v>
+      </c>
+      <c r="F455" s="7">
+        <v>250</v>
+      </c>
+      <c r="G455" s="7">
+        <f t="shared" si="103"/>
+        <v>250</v>
+      </c>
+      <c r="H455" s="7">
+        <f t="shared" si="92"/>
+        <v>75</v>
+      </c>
+      <c r="I455" s="7">
+        <f t="shared" si="100"/>
+        <v>100</v>
+      </c>
+      <c r="J455" s="7">
+        <f t="shared" si="101"/>
+        <v>25</v>
+      </c>
+      <c r="K455" s="7">
+        <f t="shared" si="102"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A456" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B456" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C456" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D456" s="7">
+        <v>3</v>
+      </c>
+      <c r="E456" s="7">
+        <v>350</v>
+      </c>
+      <c r="F456" s="7">
+        <v>500</v>
+      </c>
+      <c r="G456" s="7">
+        <f t="shared" si="103"/>
+        <v>1500</v>
+      </c>
+      <c r="H456" s="7">
+        <f t="shared" si="92"/>
+        <v>300</v>
+      </c>
+      <c r="I456" s="7">
+        <f t="shared" si="100"/>
+        <v>450</v>
+      </c>
+      <c r="J456" s="7">
+        <f t="shared" si="101"/>
+        <v>150</v>
+      </c>
+      <c r="K456" s="7">
+        <f t="shared" si="102"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A457" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B457" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C457" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D457" s="7">
+        <v>16</v>
+      </c>
+      <c r="E457" s="7">
+        <v>50</v>
+      </c>
+      <c r="F457" s="7">
+        <v>150</v>
+      </c>
+      <c r="G457" s="7">
+        <f t="shared" si="103"/>
+        <v>2400</v>
+      </c>
+      <c r="H457" s="7">
+        <f t="shared" si="92"/>
+        <v>1360</v>
+      </c>
+      <c r="I457" s="7">
+        <f t="shared" si="100"/>
+        <v>1600</v>
+      </c>
+      <c r="J457" s="7">
+        <f t="shared" si="101"/>
+        <v>240</v>
+      </c>
+      <c r="K457" s="7">
+        <f t="shared" si="102"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A458" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B458" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C458" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D458" s="7">
+        <v>8</v>
+      </c>
+      <c r="E458" s="7">
+        <v>80</v>
+      </c>
+      <c r="F458" s="7">
+        <v>250</v>
+      </c>
+      <c r="G458" s="7">
+        <f t="shared" si="103"/>
+        <v>2000</v>
+      </c>
+      <c r="H458" s="7">
+        <f t="shared" si="92"/>
+        <v>1160</v>
+      </c>
+      <c r="I458" s="7">
+        <f t="shared" si="100"/>
+        <v>1360</v>
+      </c>
+      <c r="J458" s="7">
+        <f t="shared" si="101"/>
+        <v>200</v>
+      </c>
+      <c r="K458" s="7">
+        <f t="shared" si="102"/>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A459" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B459" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C459" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D459" s="7">
+        <v>3</v>
+      </c>
+      <c r="E459" s="7">
+        <v>50</v>
+      </c>
+      <c r="F459" s="7">
+        <v>100</v>
+      </c>
+      <c r="G459" s="7">
+        <f t="shared" si="103"/>
+        <v>300</v>
+      </c>
+      <c r="H459" s="7">
+        <f t="shared" si="92"/>
+        <v>120</v>
+      </c>
+      <c r="I459" s="7">
+        <f t="shared" si="100"/>
+        <v>150</v>
+      </c>
+      <c r="J459" s="7">
+        <f t="shared" si="101"/>
+        <v>30</v>
+      </c>
+      <c r="K459" s="7">
+        <f t="shared" si="102"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A460" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B460" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C460" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D460" s="7">
+        <v>9</v>
+      </c>
+      <c r="E460" s="7">
+        <v>120</v>
+      </c>
+      <c r="F460" s="7">
+        <v>350</v>
+      </c>
+      <c r="G460" s="7">
+        <f t="shared" si="103"/>
+        <v>3150</v>
+      </c>
+      <c r="H460" s="7">
+        <f t="shared" si="92"/>
+        <v>1755</v>
+      </c>
+      <c r="I460" s="7">
+        <f t="shared" si="100"/>
+        <v>2070</v>
+      </c>
+      <c r="J460" s="7">
+        <f t="shared" si="101"/>
+        <v>315</v>
+      </c>
+      <c r="K460" s="7">
+        <f t="shared" si="102"/>
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A461" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B461" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C461" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D461" s="7">
+        <v>12</v>
+      </c>
+      <c r="E461" s="7">
+        <v>40</v>
+      </c>
+      <c r="F461" s="7">
+        <v>100</v>
+      </c>
+      <c r="G461" s="7">
+        <f t="shared" si="103"/>
+        <v>1200</v>
+      </c>
+      <c r="H461" s="7">
+        <f t="shared" si="92"/>
+        <v>600</v>
+      </c>
+      <c r="I461" s="7">
+        <f t="shared" si="100"/>
+        <v>720</v>
+      </c>
+      <c r="J461" s="7">
+        <f t="shared" si="101"/>
+        <v>120</v>
+      </c>
+      <c r="K461" s="7">
+        <f t="shared" si="102"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A462" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B462" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D462" s="7">
+        <v>1</v>
+      </c>
+      <c r="E462" s="7">
+        <v>170</v>
+      </c>
+      <c r="F462" s="7">
+        <v>200</v>
+      </c>
+      <c r="G462" s="7">
+        <f>D462*F462</f>
+        <v>200</v>
+      </c>
+      <c r="H462" s="7">
+        <f t="shared" si="92"/>
+        <v>10</v>
+      </c>
+      <c r="I462" s="7">
+        <f t="shared" si="100"/>
+        <v>30</v>
+      </c>
+      <c r="J462" s="7">
+        <f t="shared" si="101"/>
+        <v>20</v>
+      </c>
+      <c r="K462" s="7">
+        <f t="shared" si="102"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A463" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B463" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C463" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D463" s="7">
+        <v>1</v>
+      </c>
+      <c r="E463" s="7">
+        <v>150</v>
+      </c>
+      <c r="F463" s="7">
+        <v>250</v>
+      </c>
+      <c r="G463" s="7">
+        <f t="shared" ref="G463:G485" si="104">D463*F463</f>
+        <v>250</v>
+      </c>
+      <c r="H463" s="7">
+        <f t="shared" si="92"/>
+        <v>75</v>
+      </c>
+      <c r="I463" s="7">
+        <f t="shared" si="100"/>
+        <v>100</v>
+      </c>
+      <c r="J463" s="7">
+        <f t="shared" si="101"/>
+        <v>25</v>
+      </c>
+      <c r="K463" s="7">
+        <f t="shared" si="102"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A464" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B464" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C464" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D464" s="7">
+        <v>1</v>
+      </c>
+      <c r="E464" s="7">
+        <v>307</v>
+      </c>
+      <c r="F464" s="7">
+        <v>600</v>
+      </c>
+      <c r="G464" s="7">
+        <f t="shared" si="104"/>
+        <v>600</v>
+      </c>
+      <c r="H464" s="7">
+        <f t="shared" si="92"/>
+        <v>233</v>
+      </c>
+      <c r="I464" s="7">
+        <f t="shared" si="100"/>
+        <v>293</v>
+      </c>
+      <c r="J464" s="7">
+        <f t="shared" si="101"/>
+        <v>60</v>
+      </c>
+      <c r="K464" s="7">
+        <f t="shared" si="102"/>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A465" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B465" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C465" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D465" s="7">
+        <v>1</v>
+      </c>
+      <c r="E465" s="7">
+        <v>250</v>
+      </c>
+      <c r="F465" s="7">
+        <v>500</v>
+      </c>
+      <c r="G465" s="7">
+        <f t="shared" si="104"/>
+        <v>500</v>
+      </c>
+      <c r="H465" s="7">
+        <f t="shared" si="92"/>
+        <v>200</v>
+      </c>
+      <c r="I465" s="7">
+        <f t="shared" si="100"/>
+        <v>250</v>
+      </c>
+      <c r="J465" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K465" s="7">
+        <f t="shared" si="102"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A466" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B466" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C466" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D466" s="7">
+        <v>1</v>
+      </c>
+      <c r="E466" s="7">
+        <v>350</v>
+      </c>
+      <c r="F466" s="7">
+        <v>500</v>
+      </c>
+      <c r="G466" s="7">
+        <f t="shared" si="104"/>
+        <v>500</v>
+      </c>
+      <c r="H466" s="7">
+        <f t="shared" si="92"/>
+        <v>100</v>
+      </c>
+      <c r="I466" s="7">
+        <f t="shared" si="100"/>
+        <v>150</v>
+      </c>
+      <c r="J466" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K466" s="7">
+        <f t="shared" si="102"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A467" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B467" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C467" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D467" s="7">
+        <v>2</v>
+      </c>
+      <c r="E467" s="7">
+        <v>80</v>
+      </c>
+      <c r="F467" s="7">
+        <v>150</v>
+      </c>
+      <c r="G467" s="7">
+        <f>D467*F467</f>
+        <v>300</v>
+      </c>
+      <c r="H467" s="7">
+        <f t="shared" si="92"/>
+        <v>110</v>
+      </c>
+      <c r="I467" s="7">
+        <f t="shared" si="100"/>
+        <v>140</v>
+      </c>
+      <c r="J467" s="7">
+        <f t="shared" si="101"/>
+        <v>30</v>
+      </c>
+      <c r="K467" s="7">
+        <f t="shared" si="102"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A468" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B468" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C468" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D468" s="7">
+        <v>2</v>
+      </c>
+      <c r="E468" s="7">
+        <v>33</v>
+      </c>
+      <c r="F468" s="7">
+        <v>70</v>
+      </c>
+      <c r="G468" s="7">
+        <f t="shared" si="104"/>
+        <v>140</v>
+      </c>
+      <c r="H468" s="7">
+        <f t="shared" si="92"/>
+        <v>60</v>
+      </c>
+      <c r="I468" s="7">
+        <f t="shared" ref="I468" si="105">((F468-E468)*D468)-(G468*0.1)</f>
+        <v>60</v>
+      </c>
+      <c r="J468" s="7">
+        <f t="shared" ref="J468" si="106">(F468-E468)*D468</f>
+        <v>74</v>
+      </c>
+      <c r="K468" s="7">
+        <f t="shared" ref="K468" si="107">G468*0.1</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A469" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B469" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C469" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D469" s="7">
+        <v>1</v>
+      </c>
+      <c r="E469" s="7">
+        <v>400</v>
+      </c>
+      <c r="F469" s="7">
+        <v>600</v>
+      </c>
+      <c r="G469" s="7">
+        <f t="shared" si="104"/>
+        <v>600</v>
+      </c>
+      <c r="H469" s="7">
+        <f t="shared" si="92"/>
+        <v>140</v>
+      </c>
+      <c r="I469" s="7">
+        <f t="shared" si="100"/>
+        <v>200</v>
+      </c>
+      <c r="J469" s="7">
+        <f t="shared" si="101"/>
+        <v>60</v>
+      </c>
+      <c r="K469" s="7">
+        <f t="shared" si="102"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A470" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B470" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C470" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D470" s="7">
+        <v>3</v>
+      </c>
+      <c r="E470" s="7">
+        <v>30</v>
+      </c>
+      <c r="F470" s="7">
+        <v>60</v>
+      </c>
+      <c r="G470" s="7">
+        <f t="shared" si="104"/>
+        <v>180</v>
+      </c>
+      <c r="H470" s="7">
+        <f t="shared" si="92"/>
+        <v>72</v>
+      </c>
+      <c r="I470" s="7">
+        <f t="shared" si="100"/>
+        <v>90</v>
+      </c>
+      <c r="J470" s="7">
+        <f t="shared" si="101"/>
+        <v>18</v>
+      </c>
+      <c r="K470" s="7">
+        <f t="shared" si="102"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A471" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B471" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C471" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D471" s="7">
+        <v>1</v>
+      </c>
+      <c r="E471" s="7">
+        <v>350</v>
+      </c>
+      <c r="F471" s="7">
+        <v>600</v>
+      </c>
+      <c r="G471" s="7">
+        <f t="shared" si="104"/>
+        <v>600</v>
+      </c>
+      <c r="H471" s="7">
+        <f t="shared" si="92"/>
+        <v>190</v>
+      </c>
+      <c r="I471" s="7">
+        <f t="shared" si="100"/>
+        <v>250</v>
+      </c>
+      <c r="J471" s="7">
+        <f t="shared" si="101"/>
+        <v>60</v>
+      </c>
+      <c r="K471" s="7">
+        <f t="shared" si="102"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A472" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B472" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C472" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D472" s="7">
+        <v>1</v>
+      </c>
+      <c r="E472" s="7">
+        <v>700</v>
+      </c>
+      <c r="F472" s="7">
+        <v>1500</v>
+      </c>
+      <c r="G472" s="7">
+        <f t="shared" si="104"/>
+        <v>1500</v>
+      </c>
+      <c r="H472" s="7">
+        <f t="shared" si="92"/>
+        <v>650</v>
+      </c>
+      <c r="I472" s="7">
+        <f t="shared" si="100"/>
+        <v>800</v>
+      </c>
+      <c r="J472" s="7">
+        <f t="shared" si="101"/>
+        <v>150</v>
+      </c>
+      <c r="K472" s="7">
+        <f t="shared" si="102"/>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A473" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B473" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C473" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D473" s="7">
+        <v>1</v>
+      </c>
+      <c r="E473" s="7">
+        <v>100</v>
+      </c>
+      <c r="F473" s="7">
+        <v>200</v>
+      </c>
+      <c r="G473" s="7">
+        <f t="shared" si="104"/>
+        <v>200</v>
+      </c>
+      <c r="H473" s="7">
+        <f t="shared" si="92"/>
+        <v>80</v>
+      </c>
+      <c r="I473" s="7">
+        <f t="shared" si="100"/>
+        <v>100</v>
+      </c>
+      <c r="J473" s="7">
+        <f t="shared" si="101"/>
+        <v>20</v>
+      </c>
+      <c r="K473" s="7">
+        <f t="shared" si="102"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A474" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B474" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C474" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D474" s="7">
+        <v>1</v>
+      </c>
+      <c r="E474" s="7">
+        <v>200</v>
+      </c>
+      <c r="F474" s="7">
+        <v>400</v>
+      </c>
+      <c r="G474" s="7">
+        <f t="shared" si="104"/>
+        <v>400</v>
+      </c>
+      <c r="H474" s="7">
+        <f t="shared" si="92"/>
+        <v>160</v>
+      </c>
+      <c r="I474" s="7">
+        <f t="shared" si="100"/>
+        <v>200</v>
+      </c>
+      <c r="J474" s="7">
+        <f t="shared" si="101"/>
+        <v>40</v>
+      </c>
+      <c r="K474" s="7">
+        <f t="shared" si="102"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A475" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B475" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C475" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D475" s="7">
+        <v>4</v>
+      </c>
+      <c r="E475" s="7">
+        <v>80</v>
+      </c>
+      <c r="F475" s="7">
+        <v>160</v>
+      </c>
+      <c r="G475" s="7">
+        <f t="shared" si="104"/>
+        <v>640</v>
+      </c>
+      <c r="H475" s="7">
+        <f t="shared" si="92"/>
+        <v>256</v>
+      </c>
+      <c r="I475" s="7">
+        <f t="shared" si="100"/>
+        <v>320</v>
+      </c>
+      <c r="J475" s="7">
+        <f t="shared" si="101"/>
+        <v>64</v>
+      </c>
+      <c r="K475" s="7">
+        <f>D475*E475</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A476" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B476" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C476" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D476" s="7">
+        <v>21</v>
+      </c>
+      <c r="E476" s="7">
+        <v>110</v>
+      </c>
+      <c r="F476" s="7">
+        <v>180</v>
+      </c>
+      <c r="G476" s="7">
+        <f t="shared" si="104"/>
+        <v>3780</v>
+      </c>
+      <c r="H476" s="7">
+        <f t="shared" si="92"/>
+        <v>1092</v>
+      </c>
+      <c r="I476" s="7">
+        <f t="shared" si="100"/>
+        <v>1470</v>
+      </c>
+      <c r="J476" s="7">
+        <f t="shared" si="101"/>
+        <v>378</v>
+      </c>
+      <c r="K476" s="7">
+        <f t="shared" si="102"/>
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A477" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B477" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C477" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D477" s="7">
+        <v>7</v>
+      </c>
+      <c r="E477" s="7">
+        <v>220</v>
+      </c>
+      <c r="F477" s="7">
+        <v>250</v>
+      </c>
+      <c r="G477" s="7">
+        <f t="shared" si="104"/>
+        <v>1750</v>
+      </c>
+      <c r="H477" s="7">
+        <f t="shared" si="92"/>
+        <v>35</v>
+      </c>
+      <c r="I477" s="7">
+        <f t="shared" si="100"/>
+        <v>210</v>
+      </c>
+      <c r="J477" s="7">
+        <f t="shared" si="101"/>
+        <v>175</v>
+      </c>
+      <c r="K477" s="7">
+        <f t="shared" si="102"/>
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A478" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B478" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C478" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D478" s="7">
+        <v>2</v>
+      </c>
+      <c r="E478" s="7">
+        <v>100</v>
+      </c>
+      <c r="F478" s="7">
+        <v>300</v>
+      </c>
+      <c r="G478" s="7">
+        <f t="shared" si="104"/>
+        <v>600</v>
+      </c>
+      <c r="H478" s="7">
+        <f t="shared" si="92"/>
+        <v>340</v>
+      </c>
+      <c r="I478" s="7">
+        <f t="shared" si="100"/>
+        <v>400</v>
+      </c>
+      <c r="J478" s="7">
+        <f t="shared" si="101"/>
+        <v>60</v>
+      </c>
+      <c r="K478" s="7">
+        <f t="shared" si="102"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A479" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B479" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C479" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D479" s="7">
+        <v>1</v>
+      </c>
+      <c r="E479" s="7">
+        <v>150</v>
+      </c>
+      <c r="F479" s="7">
+        <v>300</v>
+      </c>
+      <c r="G479" s="7">
+        <f t="shared" si="104"/>
+        <v>300</v>
+      </c>
+      <c r="H479" s="7">
+        <f t="shared" ref="H479:H491" si="108">((F479-E479)*D479)-(G479*0.1)</f>
+        <v>120</v>
+      </c>
+      <c r="I479" s="7">
+        <f t="shared" si="100"/>
+        <v>150</v>
+      </c>
+      <c r="J479" s="7">
+        <f t="shared" si="101"/>
+        <v>30</v>
+      </c>
+      <c r="K479" s="7">
+        <f t="shared" si="102"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A480" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B480" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C480" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D480" s="7">
+        <v>1</v>
+      </c>
+      <c r="E480" s="7">
+        <v>350</v>
+      </c>
+      <c r="F480" s="7">
+        <v>500</v>
+      </c>
+      <c r="G480" s="7">
+        <f t="shared" si="104"/>
+        <v>500</v>
+      </c>
+      <c r="H480" s="7">
+        <f t="shared" si="108"/>
+        <v>100</v>
+      </c>
+      <c r="I480" s="7">
+        <f t="shared" si="100"/>
+        <v>150</v>
+      </c>
+      <c r="J480" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K480" s="7">
+        <f t="shared" si="102"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A481" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B481" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C481" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D481" s="7">
+        <v>1</v>
+      </c>
+      <c r="E481" s="7">
+        <v>300</v>
+      </c>
+      <c r="F481" s="7">
+        <v>500</v>
+      </c>
+      <c r="G481" s="7">
+        <f t="shared" si="104"/>
+        <v>500</v>
+      </c>
+      <c r="H481" s="7">
+        <f t="shared" si="108"/>
+        <v>150</v>
+      </c>
+      <c r="I481" s="7">
+        <f t="shared" si="100"/>
+        <v>200</v>
+      </c>
+      <c r="J481" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K481" s="7">
+        <f t="shared" si="102"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A482" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B482" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C482" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D482" s="7">
+        <v>1</v>
+      </c>
+      <c r="E482" s="7">
+        <v>350</v>
+      </c>
+      <c r="F482" s="7">
+        <v>500</v>
+      </c>
+      <c r="G482" s="7">
+        <f>D482*F482</f>
+        <v>500</v>
+      </c>
+      <c r="H482" s="7">
+        <f t="shared" si="108"/>
+        <v>100</v>
+      </c>
+      <c r="I482" s="7">
+        <f t="shared" si="100"/>
+        <v>150</v>
+      </c>
+      <c r="J482" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K482" s="7">
+        <f t="shared" si="102"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A483" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B483" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C483" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D483" s="7">
+        <v>1</v>
+      </c>
+      <c r="E483" s="7">
+        <v>350</v>
+      </c>
+      <c r="F483" s="7">
+        <v>500</v>
+      </c>
+      <c r="G483" s="7">
+        <f t="shared" si="104"/>
+        <v>500</v>
+      </c>
+      <c r="H483" s="7">
+        <f t="shared" si="108"/>
+        <v>100</v>
+      </c>
+      <c r="I483" s="7">
+        <f t="shared" si="100"/>
+        <v>150</v>
+      </c>
+      <c r="J483" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K483" s="7">
+        <f t="shared" si="102"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A484" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B484" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C484" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D484" s="7">
+        <v>1</v>
+      </c>
+      <c r="E484" s="7">
+        <v>250</v>
+      </c>
+      <c r="F484" s="7">
+        <v>500</v>
+      </c>
+      <c r="G484" s="7">
+        <f t="shared" si="104"/>
+        <v>500</v>
+      </c>
+      <c r="H484" s="7">
+        <f t="shared" si="108"/>
+        <v>200</v>
+      </c>
+      <c r="I484" s="7">
+        <f t="shared" si="100"/>
+        <v>250</v>
+      </c>
+      <c r="J484" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K484" s="7">
+        <f t="shared" si="102"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A485" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B485" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C485" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D485" s="7">
+        <v>1</v>
+      </c>
+      <c r="E485" s="7">
+        <v>400</v>
+      </c>
+      <c r="F485" s="7">
+        <v>600</v>
+      </c>
+      <c r="G485" s="7">
+        <f t="shared" si="104"/>
+        <v>600</v>
+      </c>
+      <c r="H485" s="7">
+        <f t="shared" si="108"/>
+        <v>140</v>
+      </c>
+      <c r="I485" s="7">
+        <f t="shared" si="100"/>
+        <v>200</v>
+      </c>
+      <c r="J485" s="7">
+        <f t="shared" si="101"/>
+        <v>60</v>
+      </c>
+      <c r="K485" s="7">
+        <f t="shared" si="102"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A486" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B486" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C486" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D486" s="7">
+        <v>4</v>
+      </c>
+      <c r="E486" s="7">
+        <v>70</v>
+      </c>
+      <c r="F486" s="7">
+        <v>100</v>
+      </c>
+      <c r="G486" s="7">
+        <f>D486*F486</f>
+        <v>400</v>
+      </c>
+      <c r="H486" s="7">
+        <f t="shared" si="108"/>
+        <v>80</v>
+      </c>
+      <c r="I486" s="7">
+        <f>(F486-E486)*D486</f>
+        <v>120</v>
+      </c>
+      <c r="J486" s="7">
+        <f t="shared" si="101"/>
+        <v>40</v>
+      </c>
+      <c r="K486" s="7">
+        <f t="shared" si="102"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A487" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B487" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C487" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D487" s="7">
+        <v>1</v>
+      </c>
+      <c r="E487" s="7">
+        <v>350</v>
+      </c>
+      <c r="F487" s="7">
+        <v>500</v>
+      </c>
+      <c r="G487" s="7">
+        <f t="shared" ref="G487" si="109">D487*F487</f>
+        <v>500</v>
+      </c>
+      <c r="H487" s="7">
+        <f t="shared" si="108"/>
+        <v>100</v>
+      </c>
+      <c r="I487" s="7">
+        <f t="shared" si="100"/>
+        <v>150</v>
+      </c>
+      <c r="J487" s="7">
+        <f t="shared" si="101"/>
+        <v>50</v>
+      </c>
+      <c r="K487" s="7">
+        <f t="shared" si="102"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A488" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B488" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C488" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D488" s="7">
+        <v>5</v>
+      </c>
+      <c r="E488" s="7">
+        <v>300</v>
+      </c>
+      <c r="F488" s="7">
+        <v>600</v>
+      </c>
+      <c r="G488" s="7">
+        <f>D488*F488</f>
+        <v>3000</v>
+      </c>
+      <c r="H488" s="7">
+        <f t="shared" si="108"/>
+        <v>1200</v>
+      </c>
+      <c r="I488" s="7">
+        <f t="shared" si="100"/>
+        <v>1500</v>
+      </c>
+      <c r="J488" s="7">
+        <f t="shared" si="101"/>
+        <v>300</v>
+      </c>
+      <c r="K488" s="7">
+        <f t="shared" si="102"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A489" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B489" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C489" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D489" s="7">
+        <v>2</v>
+      </c>
+      <c r="E489" s="7">
+        <v>250</v>
+      </c>
+      <c r="F489" s="7">
+        <v>400</v>
+      </c>
+      <c r="G489" s="7">
+        <f t="shared" ref="G489:G491" si="110">D489*F489</f>
+        <v>800</v>
+      </c>
+      <c r="H489" s="7">
+        <f t="shared" si="108"/>
+        <v>220</v>
+      </c>
+      <c r="I489" s="7">
+        <f t="shared" si="100"/>
+        <v>300</v>
+      </c>
+      <c r="J489" s="7">
+        <f t="shared" si="101"/>
+        <v>80</v>
+      </c>
+      <c r="K489" s="7">
+        <f>D489*E489</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A490" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B490" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C490" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D490" s="7">
+        <v>2</v>
+      </c>
+      <c r="E490" s="7">
+        <v>350</v>
+      </c>
+      <c r="F490" s="7">
+        <v>500</v>
+      </c>
+      <c r="G490" s="7">
+        <f t="shared" si="110"/>
+        <v>1000</v>
+      </c>
+      <c r="H490" s="7">
+        <f t="shared" si="108"/>
+        <v>200</v>
+      </c>
+      <c r="I490" s="7"/>
+      <c r="J490" s="7">
+        <f t="shared" ref="J490:J491" si="111">(F490-E490)*D490</f>
+        <v>300</v>
+      </c>
+      <c r="K490" s="7">
+        <f t="shared" ref="K490:K491" si="112">G490*0.1</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A491" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B491" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C491" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D491" s="7">
+        <v>1</v>
+      </c>
+      <c r="E491" s="7">
+        <v>150</v>
+      </c>
+      <c r="F491" s="7">
+        <v>200</v>
+      </c>
+      <c r="G491" s="7">
+        <f t="shared" si="110"/>
+        <v>200</v>
+      </c>
+      <c r="H491" s="7">
+        <f t="shared" si="108"/>
+        <v>30</v>
+      </c>
+      <c r="I491" s="7"/>
+      <c r="J491" s="7">
+        <f t="shared" si="111"/>
+        <v>50</v>
+      </c>
+      <c r="K491" s="7">
+        <f t="shared" si="112"/>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
